--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,172 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>300</v>
       </c>
       <c r="I8" s="3">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -885,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -950,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E12" s="3">
         <v>37800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>47900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1137,32 +1156,32 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
@@ -1170,8 +1189,11 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1196,8 +1218,8 @@
       <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>300</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
@@ -1214,8 +1236,8 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>89900</v>
+      </c>
+      <c r="E17" s="3">
         <v>45900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>56900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-45800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-41400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-43800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-35500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-43700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,35 +1444,36 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2200</v>
+        <v>4600</v>
       </c>
       <c r="E20" s="3">
         <v>2200</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>2200</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1457,17 +1490,17 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1477,203 +1510,215 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-43300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-38800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-43500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-35300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-34300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-28700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-19100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-43600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E22" s="3">
         <v>8100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5300</v>
       </c>
       <c r="H22" s="3">
         <v>5300</v>
       </c>
       <c r="I22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J22" s="3">
         <v>3100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1800</v>
       </c>
       <c r="L22" s="3">
         <v>1800</v>
       </c>
       <c r="M22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>300</v>
       </c>
       <c r="V22" s="3">
         <v>300</v>
       </c>
       <c r="W22" s="3">
+        <v>300</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-51800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-47000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-48900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-37700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-50500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1723,22 +1768,25 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-51800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-48900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-37700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-51400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-51800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-48900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-37700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-51400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,35 +2258,38 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2200</v>
+        <v>-4600</v>
       </c>
       <c r="E32" s="3">
         <v>-2200</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>-2200</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2237,17 +2306,17 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2257,73 +2326,79 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-51800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-48900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-37700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-51400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-51800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-48900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-37700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-51400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>277900</v>
+      </c>
+      <c r="E41" s="3">
         <v>337300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>234300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>273900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>146100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>176400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>143500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>131300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>125700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>128700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>127700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,13 +2791,16 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3">
         <v>300</v>
@@ -2726,49 +2818,52 @@
         <v>300</v>
       </c>
       <c r="J43" s="3">
+        <v>300</v>
+      </c>
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>900</v>
-      </c>
-      <c r="L43" s="3">
-        <v>500</v>
       </c>
       <c r="M43" s="3">
         <v>500</v>
       </c>
       <c r="N43" s="3">
+        <v>500</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>100</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
       <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2832,138 +2927,147 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E45" s="3">
         <v>25600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>295400</v>
+      </c>
+      <c r="E46" s="3">
         <v>363300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>203300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>243800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>280500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>153800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>150400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>139100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>119000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>131300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>113400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>132200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>131900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3027,73 +3131,79 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E48" s="3">
         <v>6300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2200</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3311,13 +3430,13 @@
         <v>3200</v>
       </c>
       <c r="J52" s="3">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="K52" s="3">
         <v>1800</v>
       </c>
       <c r="L52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
@@ -3332,28 +3451,31 @@
         <v>200</v>
       </c>
       <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+      <c r="R52" s="3">
         <v>800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>307900</v>
+      </c>
+      <c r="E54" s="3">
         <v>372700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>213200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>253700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>290900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>164900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>193200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>161200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>150500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>129200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>141900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>124500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>143700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>143600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,73 +3661,77 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7600</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3639,291 +3772,306 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1900</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E59" s="3">
         <v>27900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E60" s="3">
         <v>35800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E61" s="3">
         <v>205700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>204500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>203300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>202100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>170800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>169800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>109100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>70500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>70100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>69700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30400</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>3600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>264400</v>
+      </c>
+      <c r="E66" s="3">
         <v>243100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>238000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>238600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>232800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>199900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>198100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>133800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>101000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>97600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>63900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>88300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>60600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4382,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>59500</v>
@@ -4394,16 +4561,19 @@
         <v>59500</v>
       </c>
       <c r="U70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="V70" s="3">
         <v>47500</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>38700</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-613700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-520100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-468300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-421300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-372400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-331500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-296100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-258400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-227100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-206000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-185400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-164700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-145400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-126500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-112600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-93600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-60600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-57600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-53600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E76" s="3">
         <v>129600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-24800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>58100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-35100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>52400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>91700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-126500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-112600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-93600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-60600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-57600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-53600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-51800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-48900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-37700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-51400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5059,19 +5257,19 @@
         <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
@@ -5082,8 +5280,11 @@
       <c r="W83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-54200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-42300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30800</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-26900</v>
       </c>
       <c r="J89" s="3">
         <v>-26900</v>
       </c>
       <c r="K89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="L89" s="3">
         <v>-22600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-32100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>199900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>158700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>60200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>39200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>41500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>136200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>16900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>43300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="E102" s="3">
         <v>144800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-39600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>127800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>32900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>122000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,178 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
-        <v>45199</v>
-      </c>
       <c r="F7" s="2">
-        <v>45107</v>
-      </c>
-      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="G7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>300</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,8 +900,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>81800</v>
-      </c>
-      <c r="E12" s="3">
-        <v>37800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>33900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>37100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>30200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>24700</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3">
         <v>29700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>47900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,31 +1140,34 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1159,32 +1178,32 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2800</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
@@ -1192,37 +1211,40 @@
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>300</v>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+      <c r="L15" s="3">
+        <v>300</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
@@ -1239,8 +1261,8 @@
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>89900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>45900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>41400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>43800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>35800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>30300</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>35300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>56900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-88300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-45800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-41400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-43800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-35500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-30000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>-34600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-29000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-43700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,65 +1477,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1513,235 +1546,247 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-83500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-43300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-38800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-43500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-29700</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>-34300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-19100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-17400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-43600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>8200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>8100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>3100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1800</v>
       </c>
       <c r="M22" s="3">
         <v>1800</v>
       </c>
       <c r="N22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>300</v>
       </c>
       <c r="W22" s="3">
         <v>300</v>
       </c>
       <c r="X22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-92000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-47000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-40900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>-37700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-50500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1771,22 +1816,25 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-92000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-47100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-40900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>-37700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-51400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-93600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-47100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-40900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>-37700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-51400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,31 +2114,34 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,65 +2327,68 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2329,76 +2398,82 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-93600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-47100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-40900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>-37700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-51400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-93600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-47100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-40900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>-37700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-51400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
-        <v>45199</v>
-      </c>
       <c r="F38" s="2">
-        <v>45107</v>
-      </c>
-      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="G38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,99 +2743,103 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>277900</v>
-      </c>
-      <c r="E41" s="3">
-        <v>337300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>192500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>234300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>273900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>146100</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>176400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>143500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>131300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>125700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>108000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>128700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>127700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2794,99 +2883,105 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>800</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
-        <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
-      </c>
-      <c r="H43" s="3">
-        <v>300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>300</v>
-      </c>
-      <c r="J43" s="3">
-        <v>300</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>900</v>
-      </c>
-      <c r="M43" s="3">
-        <v>500</v>
       </c>
       <c r="N43" s="3">
         <v>500</v>
       </c>
       <c r="O43" s="3">
+        <v>500</v>
+      </c>
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
-      </c>
-      <c r="R43" s="3">
-        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
       </c>
       <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2930,167 +3025,176 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>16700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>25600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2200</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>295400</v>
-      </c>
-      <c r="E46" s="3">
-        <v>363300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>203300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>243800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>280500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>153800</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>181600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>150400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>139100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>119000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>131300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>113400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>132200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>131900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3134,99 +3238,105 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>9400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>6300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>7900</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>8400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,40 +3522,43 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>3200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1800</v>
       </c>
       <c r="L52" s="3">
         <v>1800</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
@@ -3454,28 +3573,31 @@
         <v>200</v>
       </c>
       <c r="R52" s="3">
+        <v>200</v>
+      </c>
+      <c r="S52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>307900</v>
-      </c>
-      <c r="E54" s="3">
-        <v>372700</v>
-      </c>
-      <c r="F54" s="3">
-        <v>213200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>253700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>290900</v>
-      </c>
-      <c r="I54" s="3">
-        <v>164900</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>193200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>150500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>129200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>141900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>124500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>143700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>143600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9600</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,99 +3791,103 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>11000</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
-        <v>9700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>9200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>7900</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3775,303 +3908,318 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1900</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>45400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>27900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>21600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>21700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>19300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>16900</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>15000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>56300</v>
-      </c>
-      <c r="E60" s="3">
-        <v>35800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>31300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>32600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>27600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>25400</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>24200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>34700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>29800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>207000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>205700</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>204500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>203300</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>202100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>170800</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>169800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>109100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>70500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>70100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>69700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>46500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30400</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>3600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5100</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>4100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>264400</v>
-      </c>
-      <c r="E66" s="3">
-        <v>243100</v>
-      </c>
-      <c r="F66" s="3">
-        <v>238000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>238600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>232800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>199900</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>198100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>133800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>98100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>101000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>63900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>88300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>60600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,31 +4668,34 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3">
-        <v>0</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
+      <c r="D70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -4552,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>59500</v>
@@ -4564,16 +4731,19 @@
         <v>59500</v>
       </c>
       <c r="V70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="W70" s="3">
         <v>47500</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>38700</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-613700</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-520100</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-468300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-421300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-372400</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-331500</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>-296100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-258400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-227100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-206000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-185400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-164700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-145400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-127700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-126500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-112600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-93600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-60600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-57600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-53600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>43500</v>
-      </c>
-      <c r="E76" s="3">
-        <v>129600</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>58100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-35100</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>-4900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>52400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>60600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>91700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-126500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-112600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-93600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-60600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-57600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-53600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
-        <v>45199</v>
-      </c>
       <c r="F80" s="2">
-        <v>45107</v>
-      </c>
-      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="G80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-93600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-47100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-40900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>-37700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-51400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,31 +5412,32 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -5260,19 +5458,19 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-56800</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-54200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-42300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-39900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-30600</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-30800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-26900</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>-26900</v>
       </c>
       <c r="L89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="M89" s="3">
         <v>-22600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-32100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3400</v>
+        <v>-1100</v>
       </c>
       <c r="E91" s="3">
-        <v>-800</v>
+        <v>-4600</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="S91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="U91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="S94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="U94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-600</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,99 +6529,105 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>900</v>
-      </c>
-      <c r="E100" s="3">
-        <v>199900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>158700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>500</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>60200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>39200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>41500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>40500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>136200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>16900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>43300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6423,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-59400</v>
-      </c>
-      <c r="E102" s="3">
-        <v>144800</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-41800</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-39600</v>
-      </c>
-      <c r="H102" s="3">
-        <v>127800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-30300</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
         <v>32900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>122000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,184 +656,193 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="J7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>300</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -903,8 +912,11 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +986,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1016,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="D12" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>63600</v>
+      </c>
+      <c r="F12" s="3">
+        <v>81800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>37800</v>
+      </c>
+      <c r="H12" s="3">
+        <v>33900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>37100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>30200</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3">
         <v>29700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>47900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,13 +1162,16 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-2021500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1169,8 +1191,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1181,32 +1203,32 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2800</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
@@ -1214,40 +1236,43 @@
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+      <c r="M15" s="3">
+        <v>300</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
@@ -1264,8 +1289,8 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1285,8 +1310,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>-1860500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>73800</v>
+      </c>
+      <c r="F17" s="3">
+        <v>89900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>45900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>41400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>43800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>35800</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>35300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>56900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>1860600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-73800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>-34600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-43700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,41 +1513,42 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1529,17 +1565,17 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1549,247 +1585,259 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="D21" s="3">
+        <v>1863900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>-34300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-19500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-43600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F22" s="3">
+        <v>8200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="H22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>3100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1800</v>
       </c>
       <c r="N22" s="3">
         <v>1800</v>
       </c>
       <c r="O22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>300</v>
       </c>
       <c r="X22" s="3">
         <v>300</v>
       </c>
       <c r="Y22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>-37700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-50500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1819,22 +1867,25 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>-37700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-51400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>-37700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-51400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,34 +2177,37 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2188,8 +2251,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,41 +2399,44 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2381,17 +2453,17 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2401,79 +2473,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>-37700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-51400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>-37700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-51400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="J38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,105 +2832,109 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="D41" s="3">
+        <v>226900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>252500</v>
+      </c>
+      <c r="F41" s="3">
+        <v>277900</v>
+      </c>
+      <c r="G41" s="3">
+        <v>337300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>192500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>234300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>273900</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
         <v>176400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>143500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>131300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>125700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>108000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>128700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>127700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2886,105 +2978,111 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>800</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
       </c>
+      <c r="H43" s="3">
+        <v>300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>300</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="L43" s="3">
+        <v>300</v>
+      </c>
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>900</v>
-      </c>
-      <c r="N43" s="3">
-        <v>500</v>
       </c>
       <c r="O43" s="3">
         <v>500</v>
       </c>
       <c r="P43" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
-      </c>
-      <c r="S43" s="3">
-        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
       </c>
       <c r="U43" s="3">
+        <v>100</v>
+      </c>
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3028,176 +3126,185 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="D45" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>16700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>25600</v>
+      </c>
+      <c r="H45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="D46" s="3">
+        <v>242100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>274500</v>
+      </c>
+      <c r="F46" s="3">
+        <v>295400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>363300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>203300</v>
+      </c>
+      <c r="I46" s="3">
+        <v>243800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>280500</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
         <v>181600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>150400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>139100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>119000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>131300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>113400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>132200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>131900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7500</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3241,105 +3348,111 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="D48" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>8400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -3383,8 +3496,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,43 +3644,46 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="D52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
+      <c r="G52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="L52" s="3">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="M52" s="3">
         <v>1800</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
@@ -3576,28 +3698,31 @@
         <v>200</v>
       </c>
       <c r="S52" s="3">
+        <v>200</v>
+      </c>
+      <c r="T52" s="3">
         <v>800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3792,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="D54" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>288600</v>
+      </c>
+      <c r="F54" s="3">
+        <v>307900</v>
+      </c>
+      <c r="G54" s="3">
+        <v>372700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>213200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>253700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>290900</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>193200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>161200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>150500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>129200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>141900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>124500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>143700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>143600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,87 +3924,91 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="D57" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>9200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7600</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>5</v>
+      <c r="E58" s="3">
+        <v>3600</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>5</v>
@@ -3889,8 +4025,8 @@
       <c r="J58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3911,173 +4047,182 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>1900</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5700</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="D59" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>53400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>45400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>27900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>21600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>21700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>15000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5800</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="D60" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>71900</v>
+      </c>
+      <c r="F60" s="3">
+        <v>56300</v>
+      </c>
+      <c r="G60" s="3">
+        <v>35800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>31300</v>
+      </c>
+      <c r="I60" s="3">
+        <v>32600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>27600</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="3">
         <v>24200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>34700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>25200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>20600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4085,141 +4230,147 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>204600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>207000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>205700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>204500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>203300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>202100</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>169800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>109100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>70500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>70100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>69700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>3600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5100</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>600</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4588,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="D66" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>277000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>264400</v>
+      </c>
+      <c r="G66" s="3">
+        <v>243100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>238000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>238600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>232800</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>198100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>133800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>98100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>101000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>97600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>88300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>68600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>60600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,34 +4838,37 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K70" s="3">
-        <v>0</v>
+      <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -4722,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>59500</v>
@@ -4734,16 +4904,19 @@
         <v>59500</v>
       </c>
       <c r="W70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="X70" s="3">
         <v>47500</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>38700</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4986,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="D72" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-692400</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-613700</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-520100</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-468300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-421300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-372400</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>-296100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-258400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-227100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-206000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-185400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-164700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-145400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-127700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-126500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-112600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-93600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-60600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-57600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5282,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="D76" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F76" s="3">
+        <v>43500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>129600</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>15100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>58100</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
         <v>-4900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>60600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>75500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>91700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-126500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-112600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-93600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-60600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-57600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="J80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>-37700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-51400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,34 +5613,35 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>400</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
@@ -5461,19 +5662,19 @@
         <v>300</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -5484,8 +5685,11 @@
       <c r="Y83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6055,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-26900</v>
+      <c r="D89" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-54200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>-26900</v>
       </c>
       <c r="M89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="N89" s="3">
         <v>-22600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-32100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6159,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-4600</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6379,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="L94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6483,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6555,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,105 +6777,111 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="D100" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>38700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>900</v>
+      </c>
+      <c r="G100" s="3">
+        <v>199900</v>
+      </c>
+      <c r="H100" s="3">
+        <v>900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>158700</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>60200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>39200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>41500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>17000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>136200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>16900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>43300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6674,75 +6925,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="G102" s="3">
+        <v>144800</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>127800</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>32900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>122000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,56 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
@@ -716,70 +718,73 @@
       <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <v>100</v>
@@ -790,79 +795,82 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>67600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>63900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>38100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>37400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>5</v>
@@ -915,28 +923,31 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-37400</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>5</v>
@@ -989,8 +1000,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1017,82 +1031,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>67300</v>
+        <v>38900</v>
       </c>
       <c r="E12" s="3">
-        <v>63600</v>
+        <v>67600</v>
       </c>
       <c r="F12" s="3">
-        <v>81800</v>
+        <v>63900</v>
       </c>
       <c r="G12" s="3">
-        <v>37800</v>
+        <v>38100</v>
       </c>
       <c r="H12" s="3">
-        <v>33900</v>
+        <v>34100</v>
       </c>
       <c r="I12" s="3">
-        <v>37100</v>
-      </c>
-      <c r="J12" s="3">
+        <v>37400</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3">
         <v>30200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3">
         <v>29700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>47900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,19 +1183,22 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2021500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1194,8 +1215,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1206,32 +1227,32 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2800</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
@@ -1239,19 +1260,22 @@
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -1263,19 +1287,19 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3">
-        <v>300</v>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
+      <c r="N15" s="3">
+        <v>300</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>5</v>
@@ -1292,8 +1316,8 @@
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1313,8 +1337,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,19 +1365,20 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>-1860500</v>
+        <v>46800</v>
       </c>
       <c r="E17" s="3">
+        <v>161000</v>
+      </c>
+      <c r="F17" s="3">
         <v>73800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>89900</v>
       </c>
       <c r="G17" s="3">
         <v>45900</v>
@@ -1361,133 +1389,139 @@
       <c r="I17" s="3">
         <v>43800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>35800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>35300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>56900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1860600</v>
+        <v>-46800</v>
       </c>
       <c r="E18" s="3">
+        <v>-160900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-73800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-88300</v>
       </c>
       <c r="G18" s="3">
         <v>-45800</v>
       </c>
       <c r="H18" s="3">
-        <v>-41400</v>
+        <v>-41300</v>
       </c>
       <c r="I18" s="3">
         <v>-43800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>-35500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>-34600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-29000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-43700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,71 +1548,72 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>4600</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>2200</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1588,93 +1623,99 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1863900</v>
+        <v>-46000</v>
       </c>
       <c r="E21" s="3">
-        <v>-70200</v>
+        <v>-160400</v>
       </c>
       <c r="F21" s="3">
-        <v>-83500</v>
+        <v>-73500</v>
       </c>
       <c r="G21" s="3">
-        <v>-43300</v>
+        <v>-45700</v>
       </c>
       <c r="H21" s="3">
-        <v>-38800</v>
+        <v>-41300</v>
       </c>
       <c r="I21" s="3">
         <v>-43500</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-35300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>-34300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-28700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-18300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-14200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-17400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-43600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>8200</v>
       </c>
       <c r="G22" s="3">
         <v>8100</v>
@@ -1683,72 +1724,75 @@
         <v>7900</v>
       </c>
       <c r="I22" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>5300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>3100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1800</v>
       </c>
       <c r="O22" s="3">
         <v>1800</v>
       </c>
       <c r="P22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>300</v>
       </c>
       <c r="Y22" s="3">
         <v>300</v>
       </c>
       <c r="Z22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1858000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-78700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-92000</v>
       </c>
       <c r="G23" s="3">
         <v>-51800</v>
@@ -1759,67 +1803,70 @@
       <c r="I23" s="3">
         <v>-48900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>-40900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>-37700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-50500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1833,14 +1880,14 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1870,22 +1917,25 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,19 +2008,22 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1858000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-78700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-92000</v>
       </c>
       <c r="G26" s="3">
         <v>-51800</v>
@@ -1981,70 +2034,73 @@
       <c r="I26" s="3">
         <v>-48900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>-40900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>-37700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-51400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1858000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-78700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-93600</v>
       </c>
       <c r="G27" s="3">
         <v>-51800</v>
@@ -2055,59 +2111,62 @@
       <c r="I27" s="3">
         <v>-48900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>-40900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>-37700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-20100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-51400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2239,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2206,11 +2268,11 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2254,8 +2316,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2393,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,71 +2470,74 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-4600</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-2200</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2200</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>100</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2476,19 +2547,22 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1858000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-78700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-93600</v>
       </c>
       <c r="G33" s="3">
         <v>-51800</v>
@@ -2499,59 +2573,62 @@
       <c r="I33" s="3">
         <v>-48900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>-40900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>-37700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-51400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,19 +2701,22 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1858000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-78700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-93600</v>
       </c>
       <c r="G35" s="3">
         <v>-51800</v>
@@ -2647,75 +2727,78 @@
       <c r="I35" s="3">
         <v>-48900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>-40900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>-37700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-51400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
@@ -2726,59 +2809,62 @@
       <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2891,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,82 +2920,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>196300</v>
+      </c>
+      <c r="E41" s="3">
         <v>226900</v>
       </c>
-      <c r="E41" s="3">
-        <v>252500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>277900</v>
-      </c>
-      <c r="G41" s="3">
-        <v>337300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>192500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>234300</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>273900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="3">
         <v>176400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>143500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>131300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>125700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>108000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>128700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>127700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2933,11 +3024,11 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2981,111 +3072,117 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1400</v>
       </c>
-      <c r="E43" s="3">
-        <v>3000</v>
-      </c>
       <c r="F43" s="3">
-        <v>800</v>
-      </c>
-      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>300</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3">
-        <v>300</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>900</v>
-      </c>
-      <c r="O43" s="3">
-        <v>500</v>
       </c>
       <c r="P43" s="3">
         <v>500</v>
       </c>
       <c r="Q43" s="3">
+        <v>500</v>
+      </c>
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
-      </c>
-      <c r="T43" s="3">
-        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
       </c>
       <c r="V43" s="3">
+        <v>100</v>
+      </c>
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+        <v>8300</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3129,185 +3226,194 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13800</v>
+        <v>1800</v>
       </c>
       <c r="E45" s="3">
-        <v>19000</v>
+        <v>2100</v>
       </c>
       <c r="F45" s="3">
-        <v>16700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>25600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9200</v>
-      </c>
-      <c r="J45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>207400</v>
+      </c>
+      <c r="E46" s="3">
         <v>242100</v>
       </c>
-      <c r="E46" s="3">
-        <v>274500</v>
-      </c>
       <c r="F46" s="3">
-        <v>295400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>363300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>203300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>243800</v>
-      </c>
-      <c r="J46" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>280500</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M46" s="3">
         <v>181600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>150400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>139100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>119000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>131300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>113400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>132200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>131900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3351,82 +3457,88 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E48" s="3">
         <v>9600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
-        <v>9400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>7200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>8400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3448,14 +3560,14 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3499,8 +3611,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3688,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,8 +3765,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3656,37 +3777,37 @@
         <v>6700</v>
       </c>
       <c r="E52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F52" s="3">
         <v>4600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>3200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1800</v>
       </c>
       <c r="N52" s="3">
         <v>1800</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
@@ -3701,28 +3822,31 @@
         <v>200</v>
       </c>
       <c r="T52" s="3">
+        <v>200</v>
+      </c>
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,82 +3919,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E54" s="3">
         <v>258400</v>
       </c>
-      <c r="E54" s="3">
-        <v>288600</v>
-      </c>
       <c r="F54" s="3">
-        <v>307900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>372700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>213200</v>
-      </c>
-      <c r="I54" s="3">
-        <v>253700</v>
-      </c>
-      <c r="J54" s="3">
+        <v>28200</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>290900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
         <v>193200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>161200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>150500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>129200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>141900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>124500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>143700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>143600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9600</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4027,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,304 +4056,317 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>13000</v>
+        <v>13600</v>
       </c>
       <c r="E57" s="3">
-        <v>14800</v>
+        <v>17600</v>
       </c>
       <c r="F57" s="3">
-        <v>11000</v>
-      </c>
-      <c r="G57" s="3">
+        <v>17500</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>10900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>8300</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
-        <v>9200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>7900</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>5</v>
+      <c r="D58" s="3">
+        <v>1800</v>
       </c>
       <c r="E58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>3600</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5700</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>26000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>53400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>45400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>27900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>21600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>21700</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>19300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>15000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5800</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E60" s="3">
         <v>39100</v>
       </c>
-      <c r="E60" s="3">
-        <v>71900</v>
-      </c>
       <c r="F60" s="3">
-        <v>56300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>35800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>31300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>32600</v>
-      </c>
-      <c r="J60" s="3">
+        <v>38400</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>27600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M60" s="3">
         <v>24200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>34700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>25200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>20600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4230,147 +4374,153 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>204600</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>207000</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>205700</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>204500</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>203300</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>202100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>169800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>109100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>70500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>70100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>69700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>29200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>30400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>3600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5100</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>3200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>4100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4593,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4670,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,82 +4747,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E66" s="3">
         <v>39100</v>
       </c>
-      <c r="E66" s="3">
-        <v>277000</v>
-      </c>
       <c r="F66" s="3">
-        <v>264400</v>
-      </c>
-      <c r="G66" s="3">
-        <v>243100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>238000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>238600</v>
-      </c>
-      <c r="J66" s="3">
+        <v>39000</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>232800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M66" s="3">
         <v>198100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>133800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>98100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>101000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>97600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>63900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>88300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>60600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4855,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4930,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5007,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4867,11 +5036,11 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -4895,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>59500</v>
@@ -4907,16 +5076,19 @@
         <v>59500</v>
       </c>
       <c r="X70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="Y70" s="3">
         <v>47500</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>38700</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,82 +5161,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-58300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14400</v>
       </c>
-      <c r="E72" s="3">
-        <v>-692400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-613700</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-520100</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-468300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-421300</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>-372400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>-296100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-258400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-227100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-206000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-185400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-164700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-145400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-127700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-126500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-112600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-93600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-60600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-57600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5315,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5392,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,82 +5469,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E76" s="3">
         <v>219400</v>
       </c>
-      <c r="E76" s="3">
-        <v>11600</v>
-      </c>
       <c r="F76" s="3">
-        <v>43500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>129600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-24800</v>
+        <v>-10800</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="J76" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>58100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M76" s="3">
         <v>-4900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>60600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>91700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-126500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-112600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-93600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-60600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-57600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,24 +5623,27 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
@@ -5461,70 +5654,73 @@
       <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1858000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-78700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-93600</v>
       </c>
       <c r="G81" s="3">
         <v>-51800</v>
@@ -5535,59 +5731,62 @@
       <c r="I81" s="3">
         <v>-48900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>-40900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>-37700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-51400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,37 +5813,38 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
-      </c>
-      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
-        <v>300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -5665,19 +5865,19 @@
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1200</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -5688,8 +5888,11 @@
       <c r="Z83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5965,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6042,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6119,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6196,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6273,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-57400</v>
+        <v>-30300</v>
       </c>
       <c r="E89" s="3">
-        <v>-63100</v>
+        <v>-80100</v>
       </c>
       <c r="F89" s="3">
-        <v>-56800</v>
+        <v>-40300</v>
       </c>
       <c r="G89" s="3">
         <v>-54200</v>
       </c>
       <c r="H89" s="3">
-        <v>-42300</v>
+        <v>-55300</v>
       </c>
       <c r="I89" s="3">
-        <v>-39900</v>
-      </c>
-      <c r="J89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>-30600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-26900</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>-26900</v>
       </c>
       <c r="N89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="O89" s="3">
         <v>-22600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-32100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,19 +6381,20 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-3400</v>
       </c>
       <c r="G91" s="3">
         <v>-800</v>
@@ -6183,59 +6405,62 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6533,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,19 +6610,22 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-3400</v>
       </c>
       <c r="G94" s="3">
         <v>-800</v>
@@ -6405,59 +6636,62 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,31 +6718,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6558,8 +6793,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6870,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6947,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,111 +7024,117 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>38700</v>
+        <v>30200</v>
       </c>
       <c r="F100" s="3">
-        <v>900</v>
+        <v>41400</v>
       </c>
       <c r="G100" s="3">
         <v>199900</v>
       </c>
       <c r="H100" s="3">
-        <v>900</v>
+        <v>-25800</v>
       </c>
       <c r="I100" s="3">
-        <v>400</v>
-      </c>
-      <c r="J100" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>158700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>60200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>39200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>41500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>40500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>17000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>136200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>16900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>43300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>9800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6928,78 +7178,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-25600</v>
+        <v>-30500</v>
       </c>
       <c r="E102" s="3">
-        <v>-25400</v>
+        <v>-51100</v>
       </c>
       <c r="F102" s="3">
-        <v>-59400</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
         <v>144800</v>
       </c>
       <c r="H102" s="3">
-        <v>-41800</v>
+        <v>-81400</v>
       </c>
       <c r="I102" s="3">
-        <v>-39600</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>127800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
         <v>32900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>122000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,225 +656,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
         <v>100</v>
       </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E9" s="3">
         <v>38900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>67600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>63900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>82100</v>
+      </c>
+      <c r="I9" s="3">
         <v>38100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>34100</v>
       </c>
-      <c r="I9" s="3">
-        <v>37400</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
@@ -926,32 +931,35 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-38900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-67500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-63900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>-80500</v>
+      </c>
+      <c r="I10" s="3">
         <v>-37900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-34100</v>
       </c>
-      <c r="I10" s="3">
-        <v>-37400</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1003,8 +1011,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,85 +1043,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E12" s="3">
         <v>38900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>67600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>63900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>82100</v>
+      </c>
+      <c r="I12" s="3">
         <v>38100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>34100</v>
       </c>
-      <c r="I12" s="3">
-        <v>37400</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3">
         <v>30200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>29700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>47900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1186,25 +1201,28 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2021500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
@@ -1218,8 +1236,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1230,32 +1248,32 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>2800</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
@@ -1263,22 +1281,25 @@
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>300</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1287,22 +1308,22 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="3">
-        <v>300</v>
+      <c r="M15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
+      <c r="O15" s="3">
+        <v>300</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>5</v>
@@ -1319,8 +1340,8 @@
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1340,8 +1361,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1366,162 +1390,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E17" s="3">
         <v>46800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>73800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>89900</v>
+      </c>
+      <c r="I17" s="3">
         <v>45900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>41400</v>
       </c>
-      <c r="I17" s="3">
-        <v>43800</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>35800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>35300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>56900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-46800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-160900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-73800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-45800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-41300</v>
       </c>
-      <c r="I18" s="3">
-        <v>-43800</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>-35500</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>-34600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-29000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-17600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-43700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1549,47 +1580,48 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1606,17 +1638,17 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1626,247 +1658,259 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-46000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-160400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-73500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-45700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-41300</v>
       </c>
-      <c r="I21" s="3">
-        <v>-43500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-35300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>-34300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-28700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-19100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-14200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-17400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-43600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
         <v>5400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>8100</v>
       </c>
       <c r="G22" s="3">
         <v>8100</v>
       </c>
       <c r="H22" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J22" s="3">
         <v>7900</v>
       </c>
-      <c r="I22" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>5300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>3100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1800</v>
       </c>
       <c r="P22" s="3">
         <v>1800</v>
       </c>
       <c r="Q22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>300</v>
       </c>
       <c r="Z22" s="3">
         <v>300</v>
       </c>
       <c r="AA22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-43900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1858000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-78700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-51800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-47000</v>
       </c>
-      <c r="I23" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>-40900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>-37700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-20100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-50500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1880,17 +1924,17 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1920,22 +1964,25 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2011,162 +2058,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-43900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1858000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-78700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-51800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-47100</v>
       </c>
-      <c r="I26" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>-40900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>-37700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-19300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-20100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-51400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-43900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1858000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-78700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-51800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-47100</v>
       </c>
-      <c r="I27" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>-40900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>-37700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-20100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-51400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2242,8 +2298,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2271,11 +2330,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2319,8 +2378,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2458,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2473,47 +2538,50 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>-1800</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2530,17 +2598,17 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2550,85 +2618,91 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-43900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1858000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-78700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-51800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-47100</v>
       </c>
-      <c r="I33" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>-40900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>-37700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-20100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-51400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2704,167 +2778,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-43900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1858000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-78700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-51800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-47100</v>
       </c>
-      <c r="I35" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>-40900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>-37700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-20100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-51400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2892,8 +2975,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2921,25 +3005,26 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E41" s="3">
         <v>196300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>226900</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
+      <c r="H41" s="3">
+        <v>277900</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>5</v>
@@ -2947,59 +3032,62 @@
       <c r="J41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
         <v>273900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3">
         <v>176400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>143500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>131300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>112700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>125700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>108000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>128700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>127700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3027,11 +3115,11 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -3075,25 +3163,28 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
+      <c r="H43" s="3">
+        <v>800</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
@@ -3101,76 +3192,79 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>900</v>
-      </c>
-      <c r="P43" s="3">
-        <v>500</v>
       </c>
       <c r="Q43" s="3">
         <v>500</v>
       </c>
       <c r="R43" s="3">
+        <v>500</v>
+      </c>
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
-      </c>
-      <c r="U43" s="3">
-        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
       </c>
       <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8300</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
+      <c r="H44" s="3">
+        <v>9900</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
@@ -3178,14 +3272,14 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3229,25 +3323,28 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
+      <c r="H45" s="3">
+        <v>1100</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
@@ -3255,76 +3352,79 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>6400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E46" s="3">
         <v>207400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>242100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14200</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>5</v>
+      <c r="H46" s="3">
+        <v>295400</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>5</v>
@@ -3332,59 +3432,62 @@
       <c r="J46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
         <v>280500</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3">
         <v>181600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>150400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>139100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>119000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>131300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>113400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>132200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>131900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3409,14 +3512,14 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3460,25 +3563,28 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E48" s="3">
         <v>8400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9500</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
+      <c r="H48" s="3">
+        <v>9400</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
@@ -3486,59 +3592,62 @@
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>7200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>8400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2200</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3560,17 +3669,17 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3614,8 +3723,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3691,8 +3803,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3768,25 +3883,28 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="E52" s="3">
         <v>6700</v>
       </c>
       <c r="F52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G52" s="3">
         <v>4600</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
+      <c r="H52" s="3">
+        <v>3200</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -3794,23 +3912,23 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>3200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1800</v>
       </c>
       <c r="O52" s="3">
         <v>1800</v>
       </c>
       <c r="P52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
@@ -3825,28 +3943,31 @@
         <v>200</v>
       </c>
       <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1700</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3922,25 +4043,28 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E54" s="3">
         <v>222600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>258400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28200</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>5</v>
+      <c r="H54" s="3">
+        <v>307900</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>5</v>
@@ -3948,59 +4072,62 @@
       <c r="J54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>290900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>193200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>161200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>150500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>129200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>141900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>124500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>143700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>143600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4028,8 +4155,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4057,25 +4185,26 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E57" s="3">
         <v>13600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17500</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
+      <c r="H57" s="3">
+        <v>33800</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
@@ -4083,82 +4212,85 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>8300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>9200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -4166,8 +4298,8 @@
       <c r="L58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4188,31 +4320,34 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>1900</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5700</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4237,76 +4372,79 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>19300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>15000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5800</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E60" s="3">
         <v>44100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38400</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>5</v>
+      <c r="H60" s="3">
+        <v>56300</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>5</v>
@@ -4314,76 +4452,79 @@
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="3">
         <v>27600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3">
         <v>24200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>20600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>208100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -4392,58 +4533,61 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>202100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>169800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>109100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>70500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>70100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>69700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>29400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>46500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>30400</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>3600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5100</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4468,59 +4612,62 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>200</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4596,8 +4743,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4673,8 +4823,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4750,25 +4903,28 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E66" s="3">
         <v>44100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
+      <c r="H66" s="3">
+        <v>264400</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>5</v>
@@ -4776,59 +4932,62 @@
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>232800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>198100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>133800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>98100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>101000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>97600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>63900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>88300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>68600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>60600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4856,8 +5015,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4933,8 +5093,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5010,8 +5173,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5039,11 +5205,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -5067,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>59500</v>
@@ -5079,16 +5245,19 @@
         <v>59500</v>
       </c>
       <c r="Y70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="Z70" s="3">
         <v>47500</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>38700</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5164,25 +5333,28 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-106100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-58300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14400</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
+      <c r="H72" s="3">
+        <v>-613700</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
@@ -5190,59 +5362,62 @@
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>-372400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>-296100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-258400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-227100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-206000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-185400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-164700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-145400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-127700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-126500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-112600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-93600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-60600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-53600</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5318,8 +5493,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5395,8 +5573,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5472,85 +5653,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E76" s="3">
         <v>178500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>219400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-10800</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-7300</v>
+      <c r="H76" s="3">
+        <v>43500</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
         <v>58100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N76" s="3">
         <v>-4900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>44300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>91700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-126500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-112600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-93600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-60600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-53600</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5626,167 +5813,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-43900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1858000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-78700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-51800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-47100</v>
       </c>
-      <c r="I81" s="3">
-        <v>-48900</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>-40900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>-37700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-20100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-51400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5814,8 +6010,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5825,11 +6022,11 @@
       <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+      <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>300</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
@@ -5840,14 +6037,14 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -5868,19 +6065,19 @@
         <v>300</v>
       </c>
       <c r="T83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1200</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -5891,8 +6088,11 @@
       <c r="AA83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5968,8 +6168,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6045,8 +6248,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6122,8 +6328,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6199,8 +6408,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6276,85 +6488,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-80100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-40300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="I89" s="3">
         <v>-54200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-55300</v>
       </c>
-      <c r="I89" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>-30600</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-26900</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N89" s="3">
         <v>-26900</v>
       </c>
       <c r="O89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="P89" s="3">
         <v>-22600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-32100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6382,85 +6600,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6536,8 +6758,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6613,85 +6838,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6719,8 +6950,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6977,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6796,8 +7028,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6873,8 +7108,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6950,8 +7188,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7027,8 +7268,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7036,76 +7280,79 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>30200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>41400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>900</v>
+      </c>
+      <c r="I100" s="3">
         <v>199900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-25800</v>
       </c>
-      <c r="I100" s="3">
-        <v>27000</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>158700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>60200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>39200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>41500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>40500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>17000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>136200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>16900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>43300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7130,14 +7377,14 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7181,81 +7428,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-51100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="I102" s="3">
         <v>144800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-81400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>127800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>32900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>122000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,233 +656,240 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
         <v>1600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3">
         <v>700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
         <v>33400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>38900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>67600</v>
       </c>
-      <c r="G9" s="3">
-        <v>63900</v>
-      </c>
       <c r="H9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I9" s="3">
         <v>82100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>38100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -934,35 +941,38 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-33300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-38900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-67500</v>
       </c>
-      <c r="G10" s="3">
-        <v>-63900</v>
-      </c>
       <c r="H10" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I10" s="3">
         <v>-80500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-37900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-34100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1014,8 +1024,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,88 +1057,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E12" s="3">
         <v>33400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>38900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>67600</v>
       </c>
-      <c r="G12" s="3">
-        <v>63900</v>
-      </c>
       <c r="H12" s="3">
+        <v>59700</v>
+      </c>
+      <c r="I12" s="3">
         <v>82100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3">
         <v>30200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3">
         <v>29700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>17000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>47900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,28 +1221,31 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>68100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2021500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -1239,8 +1259,8 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1251,32 +1271,32 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2800</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>5</v>
@@ -1284,8 +1304,11 @@
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1293,16 +1316,16 @@
         <v>700</v>
       </c>
       <c r="E15" s="3">
+        <v>700</v>
+      </c>
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1311,22 +1334,22 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="3">
-        <v>300</v>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
+      <c r="P15" s="3">
+        <v>300</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>5</v>
@@ -1343,8 +1366,8 @@
       <c r="U15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1364,8 +1387,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,168 +1417,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E17" s="3">
         <v>-18000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>73800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>89900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>35800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>35300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>56900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E18" s="3">
         <v>18100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-46800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-160900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-73800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-88300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-45800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>-35500</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>-34600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-29000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-18500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-17200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-17600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-43700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,50 +1614,51 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1641,17 +1675,17 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>2700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1661,265 +1695,277 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E21" s="3">
         <v>18900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-46000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-160400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-73500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-89700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-45700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-41300</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-35300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>-34300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-18500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-19500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-14200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-17400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
         <v>5400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7900</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>5300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>3100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2300</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1800</v>
       </c>
       <c r="Q22" s="3">
         <v>1800</v>
       </c>
       <c r="R22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>200</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>300</v>
       </c>
       <c r="AA22" s="3">
         <v>300</v>
       </c>
       <c r="AB22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-43900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1858000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-78700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-93600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-47000</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>-40900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>-37700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-50500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1927,17 +1973,17 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1967,22 +2013,25 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,168 +2110,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-47900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-43900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1858000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-78700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-93600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-51800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-47100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>-40900</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>-37700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-19300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-47900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-43900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1858000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-78700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-93600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-51800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-47100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>-40900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>-37700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-20500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2359,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2333,11 +2394,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2381,8 +2442,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2525,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,50 +2608,53 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2601,17 +2671,17 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-2700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2621,88 +2691,94 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-47900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-43900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1858000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-78700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-93600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-51800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-47100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>-40900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>-37700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-19300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,173 +2857,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-47900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-43900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1858000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-78700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-93600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-51800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-47100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>-40900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>-37700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-19300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="N38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3061,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,88 +3092,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>216500</v>
+      </c>
+      <c r="E41" s="3">
         <v>152600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>196300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>226900</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3">
         <v>277900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="3">
         <v>273900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="3">
         <v>176400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>143500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>131300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>112700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>125700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>108000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>128700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>127700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3118,11 +3208,11 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3166,123 +3256,129 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>900</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>500</v>
       </c>
       <c r="R43" s="3">
         <v>500</v>
       </c>
       <c r="S43" s="3">
+        <v>500</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
-      </c>
-      <c r="V43" s="3">
-        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
       </c>
       <c r="X43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9900</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3326,168 +3422,177 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>6400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E46" s="3">
         <v>160400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>207400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>242100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>295400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M46" s="3">
         <v>280500</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O46" s="3">
         <v>181600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>150400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>139100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>119000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>131300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>113400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>132200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>131900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3515,14 +3620,14 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3566,88 +3671,94 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E48" s="3">
         <v>13500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>7200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>8400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3672,17 +3783,17 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3726,8 +3837,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3920,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,8 +4003,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3895,43 +4015,43 @@
         <v>6800</v>
       </c>
       <c r="E52" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="F52" s="3">
         <v>6700</v>
       </c>
       <c r="G52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>3200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1800</v>
       </c>
       <c r="P52" s="3">
         <v>1800</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
@@ -3946,28 +4066,31 @@
         <v>200</v>
       </c>
       <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1700</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,88 +4169,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E54" s="3">
         <v>180800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>222600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>258400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>307900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
         <v>290900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O54" s="3">
         <v>193200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>161200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>150500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>129200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>141900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>124500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>143700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>143600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9600</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4285,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,114 +4316,118 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E57" s="3">
         <v>14900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>8300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O57" s="3">
         <v>9200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2100</v>
       </c>
       <c r="H58" s="3">
         <v>2100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>5</v>
@@ -4301,8 +4435,8 @@
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4323,31 +4457,34 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>1900</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5700</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4375,160 +4512,166 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>19300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>15000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E60" s="3">
         <v>40700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>39100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M60" s="3">
         <v>27600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O60" s="3">
         <v>24200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>34700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>29800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>20600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E61" s="3">
         <v>6500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>208100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -4536,58 +4679,61 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>202100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>169800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>109100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>70500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>70100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>69700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>46500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>31900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>30400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>3600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5100</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4615,59 +4761,62 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
         <v>4100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4895,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4978,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,88 +5061,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E66" s="3">
         <v>47200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>264400</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M66" s="3">
         <v>232800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O66" s="3">
         <v>198100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>133800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>98100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>101000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>97600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>63900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>68300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>88300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5177,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5258,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5341,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5208,11 +5376,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -5236,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>59500</v>
@@ -5248,16 +5416,19 @@
         <v>59500</v>
       </c>
       <c r="Z70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="AA70" s="3">
         <v>47500</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>38700</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,88 +5507,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-149400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-106100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-58300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3">
         <v>-613700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>-372400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O72" s="3">
         <v>-296100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-258400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-227100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-206000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-185400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-164700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-145400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-127700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-126500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-112600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-93600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-60600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-57600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-53600</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5673,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5756,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,88 +5839,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E76" s="3">
         <v>133600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>178500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>219400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-10800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M76" s="3">
         <v>58100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O76" s="3">
         <v>-4900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>44300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>60600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>91700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-126500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-112600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-93600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-60600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-57600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-53600</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,173 +6005,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N80" s="2">
+      <c r="N80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-47900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-43900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1858000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-78700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-93600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-51800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-47100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>-40900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>-37700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-19300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,13 +6209,14 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -6028,8 +6227,8 @@
       <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
+      <c r="H83" s="3">
+        <v>300</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>5</v>
@@ -6040,14 +6239,14 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
@@ -6068,19 +6267,19 @@
         <v>300</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -6091,8 +6290,11 @@
       <c r="AB83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6373,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6456,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6539,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6622,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,88 +6705,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-43700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-80100</v>
       </c>
-      <c r="G89" s="3">
-        <v>-40300</v>
-      </c>
       <c r="H89" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-56800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-54200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-55300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>-30600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-26900</v>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O89" s="3">
         <v>-26900</v>
       </c>
       <c r="P89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-22400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,8 +6821,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6610,79 +6831,82 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6985,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,8 +7068,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6850,79 +7080,82 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7184,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6980,8 +7214,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7031,8 +7265,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7348,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7431,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,88 +7514,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>99800</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>30200</v>
       </c>
-      <c r="G100" s="3">
-        <v>41400</v>
-      </c>
       <c r="H100" s="3">
+        <v>38700</v>
+      </c>
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>199900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>158700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>60200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>39200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>41500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>40500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>136200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>16900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>43300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7380,14 +7629,14 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -7431,84 +7680,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-43700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-51100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="I102" s="3">
         <v>-59400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>144800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-81400</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>127800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
         <v>32900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>122000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,243 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>33400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>38900</v>
       </c>
-      <c r="G9" s="3">
-        <v>67600</v>
-      </c>
       <c r="H9" s="3">
+        <v>29200</v>
+      </c>
+      <c r="I9" s="3">
         <v>4200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>82100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>38100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -944,38 +951,41 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-33300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-38900</v>
       </c>
-      <c r="G10" s="3">
-        <v>-67500</v>
-      </c>
       <c r="H10" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="I10" s="3">
         <v>-4200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-80500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-37900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-34100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1027,8 +1037,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1058,91 +1071,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E12" s="3">
         <v>35600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>38900</v>
       </c>
-      <c r="G12" s="3">
-        <v>67600</v>
-      </c>
       <c r="H12" s="3">
+        <v>38400</v>
+      </c>
+      <c r="I12" s="3">
         <v>59700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>82100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>30200</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <v>29700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>19000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>17000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>47900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,31 +1241,34 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>68100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2021500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1262,8 +1282,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1274,32 +1294,32 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2800</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>5</v>
@@ -1307,8 +1327,11 @@
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1319,16 +1342,16 @@
         <v>700</v>
       </c>
       <c r="F15" s="3">
+        <v>700</v>
+      </c>
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1337,22 +1360,22 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="3">
-        <v>300</v>
+      <c r="O15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P15" s="3">
         <v>300</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
+      <c r="Q15" s="3">
+        <v>300</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
@@ -1369,8 +1392,8 @@
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1390,8 +1413,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1418,174 +1444,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E17" s="3">
         <v>42900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-18000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>46800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>161000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>73800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>89900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>35800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>35300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>29900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>56900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-42900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-46800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-160900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-73800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-88300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-45800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-41300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>-35500</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>-34600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-17200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-43700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1615,53 +1648,54 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1678,17 +1712,17 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>2700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1698,277 +1732,289 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-42300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-46000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-160400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-73500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-89700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-45700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-41300</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-35300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>-34300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-19500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-18300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-14200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-43600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E22" s="3">
         <v>2700</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
         <v>5400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7900</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>5300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>3100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1800</v>
       </c>
       <c r="R22" s="3">
         <v>1800</v>
       </c>
       <c r="S22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>300</v>
       </c>
       <c r="AB22" s="3">
         <v>300</v>
       </c>
       <c r="AC22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-43300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-47900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-43900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1858000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-78700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-93600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-47000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>-40900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>-37700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-20000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-50500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1976,17 +2022,17 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2016,22 +2062,25 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2113,174 +2162,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-43300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-43900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1858000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-78700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-93600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-47100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>-40900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>-37700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-19300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-20000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-17900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-51400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-43300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-43900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1858000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-78700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-93600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-47100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>-40900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>-37700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-19300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-20500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-51400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2362,8 +2420,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2397,11 +2458,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2445,8 +2506,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2528,8 +2592,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2611,53 +2678,56 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2674,17 +2744,17 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-2700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2694,91 +2764,97 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-43300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-43900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1858000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-78700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-93600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-51800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-47100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>-40900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>-37700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-19300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-20500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-51400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2860,179 +2936,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-43300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-43900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1858000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-78700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-93600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-51800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-47100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>-40900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>-37700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-19300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-20500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-51400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3062,8 +3147,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3093,91 +3179,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>186600</v>
+      </c>
+      <c r="E41" s="3">
         <v>216500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>152600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>196300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>226900</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>277900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3">
         <v>273900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P41" s="3">
         <v>176400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>143500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>131300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>112700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>125700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>128700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>127700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3211,11 +3301,11 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3259,129 +3349,135 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>500</v>
       </c>
       <c r="S43" s="3">
         <v>500</v>
       </c>
       <c r="T43" s="3">
+        <v>500</v>
+      </c>
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
-      </c>
-      <c r="W43" s="3">
-        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
       </c>
       <c r="Y43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="3">
         <v>400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2400</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3425,174 +3521,183 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>6400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2200</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E46" s="3">
         <v>223400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>160400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>242100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>295400</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3">
         <v>280500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P46" s="3">
         <v>181600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>150400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>139100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>119000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>131300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>113400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>132200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>131900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3623,14 +3728,14 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3674,91 +3779,97 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E48" s="3">
         <v>12500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>7200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>8400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2200</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3786,17 +3897,17 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3840,8 +3951,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3923,8 +4037,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4006,8 +4123,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4018,43 +4138,43 @@
         <v>6800</v>
       </c>
       <c r="F52" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="G52" s="3">
         <v>6700</v>
       </c>
       <c r="H52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I52" s="3">
         <v>4600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>3200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1800</v>
       </c>
       <c r="Q52" s="3">
         <v>1800</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
@@ -4069,28 +4189,31 @@
         <v>200</v>
       </c>
       <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
         <v>800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1700</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4172,91 +4295,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212100</v>
+      </c>
+      <c r="E54" s="3">
         <v>242600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>180800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>222600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>258400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>307900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>290900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P54" s="3">
         <v>193200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>161200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>150500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>129200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>141900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>124500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>143700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>143600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9600</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4286,8 +4415,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4317,120 +4447,124 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E57" s="3">
         <v>17600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>8300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>9200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7600</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2100</v>
       </c>
       <c r="I58" s="3">
         <v>2100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
@@ -4438,8 +4572,8 @@
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4460,31 +4594,34 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>1900</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>3600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5700</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4515,142 +4652,148 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>19300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>15000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5800</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E60" s="3">
         <v>43600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>39100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3">
         <v>27600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P60" s="3">
         <v>24200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>34700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>25200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>20600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19100</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4658,23 +4801,23 @@
         <v>104600</v>
       </c>
       <c r="E61" s="3">
+        <v>104600</v>
+      </c>
+      <c r="F61" s="3">
         <v>6500</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>208100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -4682,58 +4825,61 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>202100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>169800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>109100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>70500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>70100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>46500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>30400</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>3600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5100</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4764,59 +4910,62 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>4100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4898,8 +5047,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4981,8 +5133,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5064,91 +5219,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E66" s="3">
         <v>148200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>264400</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>232800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3">
         <v>198100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>133800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>98100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>101000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>97600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>63900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>88300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>68600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>60600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24500</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5178,8 +5339,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5261,8 +5423,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5344,8 +5509,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5379,11 +5547,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O70" s="3">
-        <v>0</v>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -5407,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>59500</v>
@@ -5419,16 +5587,19 @@
         <v>59500</v>
       </c>
       <c r="AA70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="AB70" s="3">
         <v>47500</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>38700</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5510,91 +5681,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-178100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-149400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-106100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-58300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-14400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>-613700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>-372400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>-296100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-258400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-227100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-206000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-185400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-164700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-145400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-127700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-126500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-112600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-93600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-60600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-57600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-53600</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5676,8 +5853,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5759,8 +5939,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5842,91 +6025,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E76" s="3">
         <v>94400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>133600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>178500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>219400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-10800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N76" s="3">
         <v>58100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P76" s="3">
         <v>-4900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>60600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>75500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>91700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-126500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-112600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-93600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-60600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-57600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-53600</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6008,179 +6197,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O80" s="2">
+      <c r="O80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-43300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-43900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1858000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-78700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-93600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-51800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-47100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>-40900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>-37700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-19300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-20500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-51400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6210,16 +6408,17 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -6230,8 +6429,8 @@
       <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+      <c r="I83" s="3">
+        <v>300</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>5</v>
@@ -6242,14 +6441,14 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
@@ -6270,19 +6469,19 @@
         <v>300</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
       <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
@@ -6293,8 +6492,11 @@
       <c r="AC83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6376,8 +6578,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6459,8 +6664,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6542,8 +6750,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6625,8 +6836,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6708,91 +6922,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-43700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-80100</v>
-      </c>
       <c r="H89" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-63100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-56800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-54200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-55300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>-30600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-26900</v>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P89" s="3">
         <v>-26900</v>
       </c>
       <c r="Q89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="R89" s="3">
         <v>-22600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-22400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-13900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6822,8 +7042,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6834,79 +7055,82 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6988,8 +7212,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7071,8 +7298,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7083,79 +7313,82 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7185,8 +7418,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7217,8 +7451,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7268,8 +7502,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7351,8 +7588,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7434,8 +7674,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7517,91 +7760,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>99800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>33000</v>
+      </c>
+      <c r="I100" s="3">
         <v>38700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>199900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>158700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>60200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>39200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>41500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>40500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>17000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>136200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>16900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>43300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>6700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7632,14 +7881,14 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7683,87 +7932,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E102" s="3">
         <v>63900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-43700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30500</v>
       </c>
-      <c r="G102" s="3">
-        <v>-51100</v>
-      </c>
       <c r="H102" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-25400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>144800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-81400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>127800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>32900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>122000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
   <si>
     <t>INBX</t>
   </si>
@@ -656,138 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -795,13 +802,13 @@
         <v>5</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
         <v>1300</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>5</v>
@@ -813,109 +820,115 @@
         <v>5</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>1600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>13200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>8500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F9" s="3">
         <v>28500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>22300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>36900</v>
       </c>
-      <c r="G9" s="3">
-        <v>59300</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>33400</v>
+      </c>
+      <c r="J9" s="3">
         <v>38900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>67600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>63900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>82100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>38100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>34100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -964,47 +977,53 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-28500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-21000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-36900</v>
       </c>
-      <c r="G10" s="3">
-        <v>-59200</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="J10" s="3">
         <v>-38900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-67500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-63900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-80500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-37900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-34100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1053,8 +1072,14 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1086,97 +1111,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F12" s="3">
         <v>28500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>22300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>36900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>33400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>38900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>67600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>63900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>82100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>38100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>34100</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3">
         <v>30200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3">
         <v>29700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>24600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>18600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>18500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>17900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>16400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>17700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>19800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>19000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>17000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>47900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>10700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>4700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>9500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1297,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1278,26 +1317,26 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>-41100</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2021500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
@@ -1308,11 +1347,11 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1320,14 +1359,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
@@ -1335,79 +1374,85 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2800</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
       </c>
-      <c r="E15" s="3">
-        <v>700</v>
-      </c>
       <c r="F15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>700</v>
       </c>
       <c r="H15" s="3">
+        <v>700</v>
+      </c>
+      <c r="I15" s="3">
+        <v>700</v>
+      </c>
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>300</v>
-      </c>
-      <c r="L15" s="3">
-        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>300</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3">
         <v>300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
         <v>300</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
+      <c r="T15" s="3">
+        <v>300</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
@@ -1421,11 +1466,11 @@
       <c r="X15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1442,8 +1487,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1523,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>30900</v>
+      </c>
+      <c r="F17" s="3">
         <v>33800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>28700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>42900</v>
       </c>
-      <c r="G17" s="3">
-        <v>91200</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J17" s="3">
         <v>46800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>161000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>73800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>89900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>45900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>41400</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>35800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>35300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>29900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>22300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>21300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>20800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>19400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>19900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>21500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>20500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>18500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>56900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>12100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>10600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-33800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-27400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-42900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-91100</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-46800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-160900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-73800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-88300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-45800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-41300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-35500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>-34600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-29000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-19400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-18800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-19800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-18500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-17100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-17200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-43700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,8 +1748,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1692,53 +1759,53 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1752,295 +1819,319 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>2700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-33300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-27000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-42300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-90300</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-46000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-160400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-73500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-89700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-45700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-41300</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-35300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>-34300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-28700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-19100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-18500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-19500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-18300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-16800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-17400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-43600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="3">
         <v>3200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G22" s="3">
         <v>3100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>5400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>8100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>8200</v>
       </c>
       <c r="L22" s="3">
         <v>8100</v>
       </c>
       <c r="M22" s="3">
+        <v>8200</v>
+      </c>
+      <c r="N22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="O22" s="3">
         <v>7900</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>3100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>4400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>3400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>2500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>5700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-35300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-28700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-43300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-47900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-43900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1858000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-78700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-93600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-51800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-47000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-40900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>-37700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-31300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-21200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-20600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-20700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-19300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-17600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-50500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2068,14 +2159,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -2086,8 +2177,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2114,22 +2205,28 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2314,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-35300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-28700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-43300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-47900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-43900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1858000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-78700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-93600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-51800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-47100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-40900</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>-37700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-31300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-21200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-20600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-20700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-19300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-17600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-35300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-28700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-43300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-47900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-43900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1858000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-78700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-93600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-51800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-47100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-40900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>-37700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-31300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-21200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-20600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-20700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-19300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-17600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2599,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2525,14 +2646,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2573,8 +2694,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2789,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,8 +2884,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2760,53 +2899,53 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2820,117 +2959,129 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-35300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-28700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-43300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-47900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-43900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1858000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-78700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-93600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-51800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-47100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-40900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>-37700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-31300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-21200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-20600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-20700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-19300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-17600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3169,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-35300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-28700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-43300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-47900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-43900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1858000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-78700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-93600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-51800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-47100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-40900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>-37700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-31300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-21200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-20600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-20700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-19300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-17600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3403,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3438,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>161700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>124200</v>
+      </c>
+      <c r="F41" s="3">
         <v>153100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>186600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>216500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>152600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>196300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>226900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="3">
         <v>277900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="3">
         <v>273900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="3">
         <v>176400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>143500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>131300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>112700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>125700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>108000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>128700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>127700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>5600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>11500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>6200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3397,14 +3576,14 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3445,46 +3624,52 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>300</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
@@ -3492,88 +3677,94 @@
       <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3">
+        <v>300</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>2400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>9900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
@@ -3581,8 +3772,8 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3623,186 +3814,204 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E45" s="3">
         <v>1500</v>
       </c>
       <c r="F45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>6400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>6900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>5800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>5100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>3000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2200</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>132800</v>
+      </c>
+      <c r="F46" s="3">
         <v>161400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>194000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>223400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>160400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>207400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>242100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>295400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="3">
         <v>280500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="3">
         <v>181600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>150400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>139100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>119000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>131300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>113400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>132200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>131900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>8800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>15600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>10500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>5700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>7500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3839,8 +4048,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
@@ -3848,8 +4057,8 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3890,97 +4099,109 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F48" s="3">
         <v>10300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>11300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>12500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>13500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>7200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>8400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>8900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>9500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>9900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>10400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>10900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>11300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>11500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>11700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>11900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>10700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>10800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2200</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4014,8 +4235,8 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -4026,8 +4247,8 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -4068,8 +4289,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4384,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,46 +4479,52 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F52" s="3">
         <v>5700</v>
-      </c>
-      <c r="E52" s="3">
-        <v>6800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>6800</v>
       </c>
       <c r="G52" s="3">
         <v>6800</v>
       </c>
       <c r="H52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
-        <v>3200</v>
+      <c r="O52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
@@ -4293,17 +4532,17 @@
       <c r="Q52" s="3">
         <v>3200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T52" s="3">
         <v>1800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>200</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
@@ -4315,28 +4554,34 @@
         <v>200</v>
       </c>
       <c r="Y52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA52" s="3">
         <v>800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1700</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4669,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>146500</v>
+      </c>
+      <c r="F54" s="3">
         <v>177500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>212100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>242600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>180800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>222600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>258400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>28200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>307900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="3">
         <v>290900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3">
         <v>193200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>161200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>150500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>129200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>141900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>124500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>143700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>143600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>21300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>26500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>24000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>10000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>9600</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4803,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,144 +4838,152 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F57" s="3">
         <v>12700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>16700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>17600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>17600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>17500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>33800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>8300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>9200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>7900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>9100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>12400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>9900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>14300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>13500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>15200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>9400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>6500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>7600</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4734,31 +5001,37 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1900</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>3600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>8100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>5900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>5700</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4795,237 +5068,255 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>19300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>15000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>12200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>13300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>11800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>13600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>17900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>17700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>20900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>15900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>13900</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>5800</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>3700</v>
       </c>
       <c r="AD59" s="3">
         <v>5800</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>33800</v>
+      </c>
+      <c r="F60" s="3">
         <v>36000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>38900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>43600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>40700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>44100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>39100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>38400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>56300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="3">
         <v>27600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="3">
         <v>24200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>20100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>22500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>25200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>21700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>27900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>31400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>34700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>29800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>25200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>20600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>17600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>16200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>19100</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E61" s="3">
         <v>104700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>104700</v>
+      </c>
+      <c r="G61" s="3">
         <v>104600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>104600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6500</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>208100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>202100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>169800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>109100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>70500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>70100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>69700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>29400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>29200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>9800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>46500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>31900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>30400</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>3600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>5100</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5062,59 +5353,65 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
         <v>3200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3">
         <v>4100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>6200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>6600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>7600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>7300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>12000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>11500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>9600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>7500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>200</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5499,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5594,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5689,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>138500</v>
+      </c>
+      <c r="F66" s="3">
         <v>140600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>143600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>148200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>47200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>44100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>39100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>39000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>264400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q66" s="3">
         <v>232800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>198100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>133800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>98100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>101000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>97600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>63900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>68300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>51800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>88300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>68600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>60600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>25100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>20100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>24500</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5823,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5914,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +6009,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5721,14 +6056,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>5</v>
+      <c r="P70" s="3">
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
+      <c r="R70" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -5749,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>59500</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>59500</v>
@@ -5761,16 +6096,22 @@
         <v>59500</v>
       </c>
       <c r="AC70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>59500</v>
+      </c>
+      <c r="AE70" s="3">
         <v>47500</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AF70" s="3">
         <v>38700</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6199,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-279600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-246200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-213400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-178100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-149400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-106100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-58300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-14400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>-613700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-372400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>-296100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-258400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-227100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-206000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-185400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-164700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-145400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-127700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-126500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-112600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-60600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-57600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-53600</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6389,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6484,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6579,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F76" s="3">
         <v>36800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>68600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>94400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>133600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>178500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>219400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-10800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>43500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="3">
         <v>58100</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S76" s="3">
         <v>-4900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>27400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>52400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>28200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>44300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>60600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>75500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>91700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-126500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-112600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-60600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-57600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-53600</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6769,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-35300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-28700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-43300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-47900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-43900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1858000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-78700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-93600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-51800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-47100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-40900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>-37700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-31300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-21200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-20600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-20700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-19300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-17600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,25 +7003,27 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
@@ -6634,11 +7031,11 @@
       <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
+      <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
+        <v>300</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
@@ -6646,8 +7043,8 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>300</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
@@ -6655,8 +7052,8 @@
       <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
-        <v>300</v>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
@@ -6674,22 +7071,22 @@
         <v>300</v>
       </c>
       <c r="X83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>200</v>
       </c>
       <c r="AD83" s="3">
         <v>200</v>
@@ -6697,8 +7094,14 @@
       <c r="AE83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +7189,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7284,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7379,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7474,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7569,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-33800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-30000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-35900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-43700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-30300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-57400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-63100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-56800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-54200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-55300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-30600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>-26900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-26900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-22600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-13700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-22400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-21600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-15400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-32100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,13 +7703,15 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7282,79 +7723,85 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>-300</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-1800</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7889,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,13 +7984,19 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7549,25 +8008,25 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="O94" s="3">
         <v>-300</v>
@@ -7578,50 +8037,56 @@
       <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
-        <v>-100</v>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S94" s="3">
         <v>-300</v>
       </c>
       <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-1800</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +8118,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7691,11 +8158,11 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7742,8 +8209,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8304,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8399,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8494,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>99800</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>33000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>38700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>199900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-25800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>158700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
         <v>60200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>39200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>41500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>40500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>17000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>136200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>16900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>43300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>9800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>6700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>1100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8136,8 +8633,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
@@ -8145,8 +8642,8 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -8187,93 +8684,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-33500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-30000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>63900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-43700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-30500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-25600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-25400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-59400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>144800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-81400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>127800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>32900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>12200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>18600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-13000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>17700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-20700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>122000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>5200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>9400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-6400</v>
       </c>
     </row>
